--- a/Day-02 Network Fundamentals/summary/D-02 Q&A.xlsx
+++ b/Day-02 Network Fundamentals/summary/D-02 Q&A.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Mahmoud\Course\We Training\Day-02 Network Fundamentals\summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Mahmoud\Course\We Training\summary\Day-02 Network Fundamentals\summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{511DA16A-E1A8-46C2-84DE-7A63E1B2C9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B0D996-D602-434D-9393-DFF60743CC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5279320A-2232-47C3-AA9E-ADF8B8F7A462}"/>
   </bookViews>
   <sheets>
     <sheet name="day 2" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'day 2'!$A$1:$AL$57</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -351,34 +354,34 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2638,6 +2641,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B200B0-6A3C-4E5E-ADB6-B30504152C0A}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AO212"/>
   <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2648,14 +2652,14 @@
     <row r="1" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:41" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2664,16 +2668,16 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>6</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -2713,30 +2717,30 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="10"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="13"/>
       <c r="Y3" s="2"/>
-      <c r="Z3" s="8">
+      <c r="Z3" s="7">
         <v>11</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AA3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
@@ -2775,13 +2779,13 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
-      <c r="AA4" s="7" t="s">
+      <c r="AA4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
@@ -2805,7 +2809,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="16" t="b">
+      <c r="L5" s="9" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="2"/>
@@ -2913,11 +2917,11 @@
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
-      <c r="AG7" s="12" t="s">
+      <c r="AG7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="10"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="13"/>
       <c r="AJ7" s="2"/>
       <c r="AK7" s="2"/>
       <c r="AL7" s="2"/>
@@ -3108,37 +3112,37 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="8">
+      <c r="N12" s="7">
         <v>7</v>
       </c>
       <c r="O12" s="2"/>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
       <c r="Y12" s="2"/>
-      <c r="Z12" s="8">
+      <c r="Z12" s="7">
         <v>12</v>
       </c>
       <c r="AA12" s="2"/>
-      <c r="AB12" s="7" t="s">
+      <c r="AB12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
-      <c r="AF12" s="7"/>
-      <c r="AG12" s="7"/>
-      <c r="AH12" s="7"/>
-      <c r="AI12" s="7"/>
-      <c r="AJ12" s="7"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="15"/>
       <c r="AK12" s="2"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
@@ -3147,7 +3151,7 @@
     </row>
     <row r="13" spans="1:41" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>2</v>
       </c>
       <c r="C13" s="2"/>
@@ -3165,31 +3169,31 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
-      <c r="AB13" s="7" t="s">
+      <c r="AB13" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
-      <c r="AF13" s="7"/>
-      <c r="AG13" s="7"/>
-      <c r="AH13" s="7"/>
-      <c r="AI13" s="7"/>
-      <c r="AJ13" s="7"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="15"/>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15"/>
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="15"/>
       <c r="AK13" s="2"/>
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
@@ -3212,15 +3216,15 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="7" t="s">
+      <c r="P14" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
@@ -3304,15 +3308,15 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="12" t="s">
+      <c r="R16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="10"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="13"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
@@ -3322,11 +3326,11 @@
       <c r="AE16" s="2"/>
       <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
-      <c r="AH16" s="12" t="s">
+      <c r="AH16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AI16" s="11"/>
-      <c r="AJ16" s="10"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="13"/>
       <c r="AK16" s="2"/>
       <c r="AL16" s="2"/>
       <c r="AM16" s="2"/>
@@ -3338,11 +3342,11 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="10"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3466,55 +3470,55 @@
     </row>
     <row r="20" spans="1:41" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>3</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="8">
+      <c r="N20" s="7">
         <v>8</v>
       </c>
-      <c r="O20" s="7" t="s">
+      <c r="O20" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="7" t="s">
+      <c r="U20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="V20" s="7"/>
+      <c r="V20" s="15"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
-      <c r="Z20" s="8">
+      <c r="Z20" s="7">
         <v>13</v>
       </c>
       <c r="AA20" s="2"/>
-      <c r="AB20" s="7" t="s">
+      <c r="AB20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" s="7"/>
-      <c r="AF20" s="7"/>
-      <c r="AG20" s="7"/>
-      <c r="AH20" s="7"/>
-      <c r="AI20" s="7"/>
-      <c r="AJ20" s="7"/>
+      <c r="AC20" s="15"/>
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="15"/>
+      <c r="AF20" s="15"/>
+      <c r="AG20" s="15"/>
+      <c r="AH20" s="15"/>
+      <c r="AI20" s="15"/>
+      <c r="AJ20" s="15"/>
       <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
@@ -3524,12 +3528,12 @@
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -3551,17 +3555,17 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
-      <c r="AB21" s="7" t="s">
+      <c r="AB21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
-      <c r="AE21" s="7"/>
-      <c r="AF21" s="7"/>
-      <c r="AG21" s="7"/>
-      <c r="AH21" s="7"/>
-      <c r="AI21" s="7"/>
-      <c r="AJ21" s="7"/>
+      <c r="AC21" s="15"/>
+      <c r="AD21" s="15"/>
+      <c r="AE21" s="15"/>
+      <c r="AF21" s="15"/>
+      <c r="AG21" s="15"/>
+      <c r="AH21" s="15"/>
+      <c r="AI21" s="15"/>
+      <c r="AJ21" s="15"/>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
@@ -3616,7 +3620,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="2"/>
@@ -3678,11 +3682,11 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="12" t="s">
+      <c r="V24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="W24" s="11"/>
-      <c r="X24" s="10"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="13"/>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
@@ -3872,14 +3876,14 @@
     </row>
     <row r="29" spans="1:41" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>4</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -3888,15 +3892,15 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
-      <c r="N29" s="8">
+      <c r="N29" s="7">
         <v>9</v>
       </c>
-      <c r="O29" s="7" t="s">
+      <c r="O29" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
@@ -3924,11 +3928,11 @@
     <row r="30" spans="1:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -3938,12 +3942,12 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="7" t="s">
+      <c r="O30" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
@@ -3960,11 +3964,11 @@
       <c r="AF30" s="2"/>
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
-      <c r="AI30" s="12">
+      <c r="AI30" s="11">
         <v>1492</v>
       </c>
-      <c r="AJ30" s="11"/>
-      <c r="AK30" s="10"/>
+      <c r="AJ30" s="12"/>
+      <c r="AK30" s="13"/>
       <c r="AL30" s="2"/>
       <c r="AM30" s="2"/>
       <c r="AN30" s="2"/>
@@ -4146,13 +4150,13 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="10"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="13"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -4166,11 +4170,11 @@
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
-      <c r="V35" s="12" t="s">
+      <c r="V35" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="W35" s="11"/>
-      <c r="X35" s="10"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="13"/>
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
@@ -4461,37 +4465,37 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
-      <c r="N42" s="8">
+      <c r="N42" s="7">
         <v>10</v>
       </c>
       <c r="O42" s="2"/>
-      <c r="P42" s="7" t="s">
+      <c r="P42" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
       <c r="Y42" s="2"/>
-      <c r="Z42" s="8">
+      <c r="Z42" s="7">
         <v>14</v>
       </c>
       <c r="AA42" s="2"/>
-      <c r="AB42" s="7" t="s">
+      <c r="AB42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="7"/>
-      <c r="AE42" s="7"/>
-      <c r="AF42" s="7"/>
-      <c r="AG42" s="7"/>
-      <c r="AH42" s="7"/>
-      <c r="AI42" s="7"/>
-      <c r="AJ42" s="7"/>
+      <c r="AC42" s="15"/>
+      <c r="AD42" s="15"/>
+      <c r="AE42" s="15"/>
+      <c r="AF42" s="15"/>
+      <c r="AG42" s="15"/>
+      <c r="AH42" s="15"/>
+      <c r="AI42" s="15"/>
+      <c r="AJ42" s="15"/>
       <c r="AK42" s="2"/>
       <c r="AL42" s="2"/>
       <c r="AM42" s="2"/>
@@ -4500,49 +4504,49 @@
     </row>
     <row r="43" spans="1:41" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>5</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
-      <c r="P43" s="7" t="s">
+      <c r="P43" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
-      <c r="X43" s="7"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="15"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
-      <c r="AB43" s="7" t="s">
+      <c r="AB43" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="AC43" s="7"/>
-      <c r="AD43" s="7"/>
-      <c r="AE43" s="7"/>
-      <c r="AF43" s="7"/>
-      <c r="AG43" s="7"/>
-      <c r="AH43" s="7"/>
-      <c r="AI43" s="7"/>
-      <c r="AJ43" s="7"/>
+      <c r="AC43" s="15"/>
+      <c r="AD43" s="15"/>
+      <c r="AE43" s="15"/>
+      <c r="AF43" s="15"/>
+      <c r="AG43" s="15"/>
+      <c r="AH43" s="15"/>
+      <c r="AI43" s="15"/>
+      <c r="AJ43" s="15"/>
       <c r="AK43" s="2"/>
       <c r="AL43" s="2"/>
       <c r="AM43" s="2"/>
@@ -4623,11 +4627,11 @@
       <c r="AA45" s="2"/>
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
-      <c r="AD45" s="12" t="s">
+      <c r="AD45" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AE45" s="11"/>
-      <c r="AF45" s="10"/>
+      <c r="AE45" s="12"/>
+      <c r="AF45" s="13"/>
       <c r="AG45" s="2"/>
       <c r="AH45" s="2"/>
       <c r="AI45" s="2"/>
@@ -4660,11 +4664,11 @@
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
-      <c r="V46" s="12" t="s">
+      <c r="V46" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="W46" s="11"/>
-      <c r="X46" s="10"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="13"/>
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
@@ -4688,7 +4692,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F47" s="2"/>
@@ -4840,21 +4844,21 @@
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="2"/>
-      <c r="Z50" s="8">
+      <c r="Z50" s="7">
         <v>15</v>
       </c>
       <c r="AA50" s="2"/>
-      <c r="AB50" s="7" t="s">
+      <c r="AB50" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AC50" s="7"/>
-      <c r="AD50" s="7"/>
-      <c r="AE50" s="7"/>
-      <c r="AF50" s="7"/>
-      <c r="AG50" s="7"/>
-      <c r="AH50" s="7"/>
-      <c r="AI50" s="7"/>
-      <c r="AJ50" s="7"/>
+      <c r="AC50" s="15"/>
+      <c r="AD50" s="15"/>
+      <c r="AE50" s="15"/>
+      <c r="AF50" s="15"/>
+      <c r="AG50" s="15"/>
+      <c r="AH50" s="15"/>
+      <c r="AI50" s="15"/>
+      <c r="AJ50" s="15"/>
       <c r="AK50" s="2"/>
       <c r="AL50" s="2"/>
       <c r="AM50" s="2"/>
@@ -4889,17 +4893,17 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
-      <c r="AB51" s="7" t="s">
+      <c r="AB51" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="AC51" s="7"/>
-      <c r="AD51" s="7"/>
-      <c r="AE51" s="7"/>
-      <c r="AF51" s="7"/>
-      <c r="AG51" s="7"/>
-      <c r="AH51" s="7"/>
-      <c r="AI51" s="7"/>
-      <c r="AJ51" s="7"/>
+      <c r="AC51" s="15"/>
+      <c r="AD51" s="15"/>
+      <c r="AE51" s="15"/>
+      <c r="AF51" s="15"/>
+      <c r="AG51" s="15"/>
+      <c r="AH51" s="15"/>
+      <c r="AI51" s="15"/>
+      <c r="AJ51" s="15"/>
       <c r="AK51" s="2"/>
       <c r="AL51" s="2"/>
       <c r="AM51" s="2"/>
@@ -4934,17 +4938,17 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
-      <c r="AB52" s="7" t="s">
+      <c r="AB52" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AC52" s="7"/>
-      <c r="AD52" s="7"/>
-      <c r="AE52" s="7"/>
-      <c r="AF52" s="7"/>
-      <c r="AG52" s="7"/>
-      <c r="AH52" s="7"/>
-      <c r="AI52" s="7"/>
-      <c r="AJ52" s="7"/>
+      <c r="AC52" s="15"/>
+      <c r="AD52" s="15"/>
+      <c r="AE52" s="15"/>
+      <c r="AF52" s="15"/>
+      <c r="AG52" s="15"/>
+      <c r="AH52" s="15"/>
+      <c r="AI52" s="15"/>
+      <c r="AJ52" s="15"/>
       <c r="AK52" s="2"/>
       <c r="AL52" s="2"/>
       <c r="AM52" s="2"/>
@@ -11834,25 +11838,16 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="P14:V14"/>
-    <mergeCell ref="R16:X16"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AB51:AJ51"/>
+    <mergeCell ref="AB52:AJ52"/>
+    <mergeCell ref="AG7:AI7"/>
+    <mergeCell ref="AB20:AJ20"/>
+    <mergeCell ref="AB21:AJ21"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AB42:AJ42"/>
+    <mergeCell ref="AB12:AJ12"/>
+    <mergeCell ref="AB13:AJ13"/>
     <mergeCell ref="V46:X46"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AA4:AE4"/>
@@ -11863,18 +11858,31 @@
     <mergeCell ref="P43:X43"/>
     <mergeCell ref="P42:X42"/>
     <mergeCell ref="O20:S20"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AB51:AJ51"/>
-    <mergeCell ref="AB52:AJ52"/>
-    <mergeCell ref="AG7:AI7"/>
-    <mergeCell ref="AB20:AJ20"/>
-    <mergeCell ref="AB21:AJ21"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AB42:AJ42"/>
-    <mergeCell ref="AB12:AJ12"/>
-    <mergeCell ref="AB13:AJ13"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="P12:X12"/>
+    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="P14:V14"/>
+    <mergeCell ref="R16:X16"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:E29"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0" right="0.2" top="0.2" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="19" scale="29" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="38" max="58" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>